--- a/real_estate_agent_forms/001_lease_renewal_information_update_form--real_estate_agent_forms.xlsx
+++ b/real_estate_agent_forms/001_lease_renewal_information_update_form--real_estate_agent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>lease_status</t>
+          <t>lease_status_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lease Status</t>
+          <t>Lease Status 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rent_frequency</t>
+          <t>rent_frequency_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rent Frequency</t>
+          <t>Rent Frequency 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rent_amount</t>
+          <t>rent_amount_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rent Amount</t>
+          <t>Rent Amount 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lease_status_choices</t>
+          <t>lease_status_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lease_status_choices</t>
+          <t>lease_status_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rent_frequency_choices</t>
+          <t>rent_frequency_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rent_frequency_choices</t>
+          <t>rent_frequency_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
